--- a/RANCANGAN_FELDA_KIT_GAJAH_2026.xlsx
+++ b/RANCANGAN_FELDA_KIT_GAJAH_2026.xlsx
@@ -829,7 +829,7 @@
       </c>
     </row>
     <row r="13" spans="2:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="3"/>
+      <c r="B13" s="2"/>
       <c r="C13" s="9">
         <v>10</v>
       </c>
@@ -838,7 +838,9 @@
       </c>
     </row>
     <row r="14" spans="2:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="2"/>
+      <c r="B14" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="C14" s="9">
         <v>11</v>
       </c>
@@ -847,9 +849,7 @@
       </c>
     </row>
     <row r="15" spans="2:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="1" t="s">
-        <v>14</v>
-      </c>
+      <c r="B15" s="3"/>
       <c r="C15" s="9">
         <v>12</v>
       </c>
@@ -1149,9 +1149,9 @@
     <mergeCell ref="B23:B29"/>
     <mergeCell ref="B30:B33"/>
     <mergeCell ref="B34:B36"/>
-    <mergeCell ref="B15:B20"/>
+    <mergeCell ref="B14:B20"/>
     <mergeCell ref="B21:B22"/>
-    <mergeCell ref="B4:B14"/>
+    <mergeCell ref="B4:B13"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="D2:D3"/>
